--- a/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513262_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513262_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. VRANKIC</t>
+          <t>A. WINTERING</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4825</v>
+        <v>2.8679</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6318</v>
+        <v>3.4378</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8507</v>
+        <v>-0.5698</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6067</v>
+        <v>0.2003</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3066</v>
+        <v>-2.23</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6999</v>
+        <v>2.4303</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9096</v>
+        <v>1.6</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8933</v>
+        <v>-1.9479</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0163</v>
+        <v>3.5478</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3029</v>
+        <v>-1.3997</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4133</v>
+        <v>-0.2821</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-1.1176</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.9825</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.5244</v>
+        <v>-1.1014</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5419</v>
+        <v>1.1014</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1798</v>
+        <v>0.9893</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4492</v>
+        <v>0.7013</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7306</v>
+        <v>0.2879</v>
       </c>
       <c r="V2" t="n">
         <v>1.6784</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7973</v>
+        <v>2.2378</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1189</v>
+        <v>-0.5595</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. WINTERING</t>
+          <t>J. VRANKIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4281</v>
+        <v>2.3772</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9691</v>
+        <v>1.7571</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.541</v>
+        <v>0.6201</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2003</v>
+        <v>0.6067</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.23</v>
+        <v>1.3066</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4303</v>
+        <v>-0.6999</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6</v>
+        <v>0.9096</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.9479</v>
+        <v>0.8933</v>
       </c>
       <c r="L3" t="n">
-        <v>3.5478</v>
+        <v>0.0163</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3997</v>
+        <v>-0.3029</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2821</v>
+        <v>0.4133</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1176</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-1.9825</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1014</v>
+        <v>-3.5244</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1014</v>
+        <v>1.5419</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5494</v>
+        <v>2.0746</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2327</v>
+        <v>1.5746</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3167</v>
+        <v>0.5</v>
       </c>
       <c r="V3" t="n">
         <v>1.6784</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2378</v>
+        <v>2.7973</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5595</v>
+        <v>-1.1189</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MUNOZ BORCHERS</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7916</v>
+        <v>2.1118</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0691</v>
+        <v>2.1569</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2775</v>
+        <v>-0.0451</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5616</v>
+        <v>1.4554</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7038</v>
+        <v>0.7935</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2654</v>
+        <v>0.6619</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4719</v>
+        <v>2.8518</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.6927</v>
       </c>
       <c r="L4" t="n">
-        <v>3.4719</v>
+        <v>2.1592</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9102</v>
+        <v>-1.3964</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7038</v>
+        <v>0.1008</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2065</v>
+        <v>-1.4973</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.8811</v>
+        <v>-1.1014</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1014</v>
+        <v>-2.2027</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2203</v>
+        <v>1.1014</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7366</v>
+        <v>0.2644</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4203</v>
+        <v>0.3889</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1569</v>
+        <v>-0.1245</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3745</v>
+        <v>1.4934</v>
       </c>
       <c r="W4" t="n">
         <v>1.1189</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7444</v>
+        <v>0.3745</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>A. MUNOZ BORCHERS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5191</v>
+        <v>1.5936</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7846</v>
+        <v>3.3035</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7346</v>
+        <v>-1.7099</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1434</v>
+        <v>1.5616</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4382</v>
+        <v>-0.7038</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5816</v>
+        <v>2.2654</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4015</v>
+        <v>3.4719</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.358</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7595</v>
+        <v>3.4719</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5448</v>
+        <v>-1.9102</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7962</v>
+        <v>-0.7038</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3411</v>
+        <v>-1.2065</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.8811</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1014</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4405</v>
+        <v>0.2203</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8828</v>
+        <v>0.5386</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8589</v>
+        <v>-0.186</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0238</v>
+        <v>0.7245</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5595</v>
+        <v>0.3745</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3745</v>
+        <v>1.1189</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.185</v>
+        <v>-0.7444</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1077</v>
+        <v>1.1979</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7532</v>
+        <v>0.9875</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3545</v>
+        <v>0.2104</v>
       </c>
       <c r="G6" t="n">
         <v>0.2508</v>
@@ -922,13 +922,13 @@
         <v>0.6608000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4164</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2</v>
+        <v>0.0343</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.4722</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9727</v>
+        <v>0.4396</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2196</v>
+        <v>-0.0356</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2469</v>
+        <v>0.4751</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4554</v>
+        <v>-0.1434</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7935</v>
+        <v>0.4382</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6619</v>
+        <v>-0.5816</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8518</v>
+        <v>0.4015</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6927</v>
+        <v>-0.358</v>
       </c>
       <c r="L7" t="n">
-        <v>2.1592</v>
+        <v>0.7595</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3964</v>
+        <v>-0.5448</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1008</v>
+        <v>0.7962</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4973</v>
+        <v>-1.3411</v>
       </c>
       <c r="P7" t="n">
+        <v>-0.6608000000000001</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-1.1014</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-2.2027</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.1014</v>
+        <v>0.4405</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8747</v>
+        <v>1.8032</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5484</v>
+        <v>1.0388</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3263</v>
+        <v>0.7644</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4934</v>
+        <v>-0.5595</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1189</v>
+        <v>-0.3745</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3745</v>
+        <v>-0.185</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. VUCETIC</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5714</v>
+        <v>0.4193</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0067</v>
+        <v>1.776</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5648</v>
+        <v>-1.3567</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1815</v>
+        <v>1.742</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6996</v>
+        <v>-0.5959</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4819</v>
+        <v>2.338</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5131</v>
+        <v>1.6215</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3871</v>
+        <v>-0.6732</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.9003</v>
+        <v>2.2947</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6683</v>
+        <v>0.1206</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0867</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5816</v>
+        <v>0.0433</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1014</v>
+        <v>0.2203</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.2203</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3216</v>
+        <v>0.4405</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4253</v>
+        <v>0.6948</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3922</v>
+        <v>0.3749</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0331</v>
+        <v>0.32</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9339</v>
+        <v>-2.2378</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1189</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.185</v>
+        <v>-2.2378</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>V. VUCETIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6584</v>
+        <v>-0.047</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0731</v>
+        <v>0.3448</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7315</v>
+        <v>-0.3918</v>
       </c>
       <c r="G9" t="n">
-        <v>1.742</v>
+        <v>-2.1815</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5959</v>
+        <v>-0.6996</v>
       </c>
       <c r="I9" t="n">
-        <v>2.338</v>
+        <v>-1.4819</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6215</v>
+        <v>-0.5131</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6732</v>
+        <v>0.3871</v>
       </c>
       <c r="L9" t="n">
-        <v>2.2947</v>
+        <v>-0.9003</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1206</v>
+        <v>-1.6683</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07729999999999999</v>
+        <v>-1.0867</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0433</v>
+        <v>-0.5816</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2203</v>
+        <v>1.1014</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.2203</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4405</v>
+        <v>1.3216</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3829</v>
+        <v>0.0992</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3281</v>
+        <v>-0.0407</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0548</v>
+        <v>0.1399</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.2378</v>
+        <v>0.9339</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.1189</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.2378</v>
+        <v>-0.185</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0092</v>
+        <v>-2.9515</v>
       </c>
       <c r="E10" t="n">
         <v>-2.2152</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-0.7363</v>
       </c>
       <c r="G10" t="n">
         <v>-3.2495</v>
@@ -1234,13 +1234,13 @@
         <v>0.4405</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.9412</v>
       </c>
       <c r="T10" t="n">
         <v>0.2967</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5868</v>
+        <v>0.6445</v>
       </c>
       <c r="V10" t="n">
         <v>1.1189</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2478</v>
+        <v>-3.1938</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8338</v>
+        <v>-4.0681</v>
       </c>
       <c r="F11" t="n">
-        <v>0.586</v>
+        <v>0.8743</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6182</v>
@@ -1312,13 +1312,13 @@
         <v>1.5419</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5249</v>
+        <v>0.5788</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2608</v>
+        <v>0.0265</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2641</v>
+        <v>0.5523</v>
       </c>
       <c r="V11" t="n">
         <v>0.9294</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.8149</v>
+        <v>4.815000000000003</v>
       </c>
       <c r="E12" t="n">
-        <v>7.444800000000001</v>
+        <v>7.444700000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6298</v>
+        <v>-2.6297</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3758</v>
@@ -1390,13 +1390,13 @@
         <v>8.8108</v>
       </c>
       <c r="S12" t="n">
-        <v>8.490600000000001</v>
+        <v>8.4907</v>
       </c>
       <c r="T12" t="n">
-        <v>4.2093</v>
+        <v>4.209300000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>4.281099999999999</v>
+        <v>4.2812</v>
       </c>
       <c r="V12" t="n">
         <v>5.4096</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.321</v>
+        <v>5.228</v>
       </c>
       <c r="E13" t="n">
-        <v>4.2348</v>
+        <v>4.1176</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0862</v>
+        <v>1.1104</v>
       </c>
       <c r="G13" t="n">
         <v>3.5705</v>
@@ -1468,13 +1468,13 @@
         <v>2.8635</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3686</v>
+        <v>-0.4616</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3798</v>
+        <v>-0.4969</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0111</v>
+        <v>0.0353</v>
       </c>
       <c r="V13" t="n">
         <v>-0.7444</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1589</v>
+        <v>3.0841</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7432</v>
+        <v>6.2119</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.5843</v>
+        <v>-3.1278</v>
       </c>
       <c r="G14" t="n">
         <v>3.5099</v>
@@ -1546,13 +1546,13 @@
         <v>2.6433</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.7034</v>
+        <v>-1.7782</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4092</v>
+        <v>-0.9406</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2942</v>
+        <v>-0.8376</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1895</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1093</v>
+        <v>-0.1176</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2886</v>
+        <v>0.0542</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3978</v>
+        <v>-0.1719</v>
       </c>
       <c r="G15" t="n">
         <v>-1.3157</v>
@@ -1624,13 +1624,13 @@
         <v>1.9825</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.406</v>
+        <v>-0.4144</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2157</v>
+        <v>-0.45</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1903</v>
+        <v>0.0356</v>
       </c>
       <c r="V15" t="n">
         <v>-0.37</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.0849</v>
+        <v>-0.6553</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4617</v>
+        <v>-1.3445</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3768</v>
+        <v>0.6893</v>
       </c>
       <c r="G16" t="n">
         <v>2.7315</v>
@@ -1702,13 +1702,13 @@
         <v>1.1014</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1203</v>
+        <v>0.3093</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4562</v>
+        <v>-0.3391</v>
       </c>
       <c r="U16" t="n">
-        <v>0.336</v>
+        <v>0.6484</v>
       </c>
       <c r="V16" t="n">
         <v>-1.4934</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7448</v>
+        <v>-1.4154</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0014</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7435</v>
+        <v>-0.7375</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4157</v>
+        <v>-0.0091</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3484</v>
+        <v>2.0751</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7641</v>
+        <v>-2.0842</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7451</v>
+        <v>0.8266</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0359</v>
+        <v>0.8102</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7811</v>
+        <v>0.0163</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6705</v>
+        <v>-0.8356</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3124</v>
+        <v>1.2649</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.983</v>
+        <v>-2.1005</v>
       </c>
       <c r="P17" t="n">
         <v>0.2203</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1014</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2203</v>
+        <v>1.3216</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5494</v>
+        <v>-0.5077</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2562</v>
+        <v>-0.4031</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2932</v>
+        <v>-0.1046</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.1189</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.1189</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8041</v>
+        <v>-1.5598</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7951</v>
+        <v>-1.0014</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.009</v>
+        <v>-0.5584</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0091</v>
+        <v>-1.4157</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0751</v>
+        <v>0.3484</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.0842</v>
+        <v>-1.7641</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8266</v>
+        <v>-0.7451</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8102</v>
+        <v>0.0359</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0163</v>
+        <v>-0.7811</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8356</v>
+        <v>-0.6705</v>
       </c>
       <c r="N18" t="n">
-        <v>1.2649</v>
+        <v>0.3124</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.1005</v>
+        <v>-0.983</v>
       </c>
       <c r="P18" t="n">
         <v>0.2203</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1014</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3216</v>
+        <v>0.2203</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8964</v>
+        <v>-0.3644</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5203</v>
+        <v>-0.2562</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3761</v>
+        <v>-0.1082</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1189</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2286</v>
+        <v>-2.2202</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2775</v>
+        <v>1.0432</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.5061</v>
+        <v>-3.2634</v>
       </c>
       <c r="G19" t="n">
         <v>-2.2163</v>
@@ -1936,13 +1936,13 @@
         <v>1.7622</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3999</v>
+        <v>-1.3916</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0516</v>
+        <v>-0.286</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.3483</v>
+        <v>-1.1056</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3745</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BELEMENE-DZABATOU</t>
+          <t>M. DIAZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3696</v>
+        <v>-2.38</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4314</v>
+        <v>-3.1076</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0618</v>
+        <v>0.7276</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9716</v>
+        <v>-1.5079</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.453</v>
+        <v>0.6153</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-2.1231</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1144</v>
+        <v>-0.2455</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.6243</v>
+        <v>-0.4464</v>
       </c>
       <c r="L20" t="n">
-        <v>0.51</v>
+        <v>0.2009</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8573</v>
+        <v>-1.2624</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1714</v>
+        <v>1.0617</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0286</v>
+        <v>-2.324</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3216</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1014</v>
+        <v>-2.2027</v>
       </c>
       <c r="R20" t="n">
-        <v>2.423</v>
+        <v>2.2027</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6007</v>
+        <v>-0.8721</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2157</v>
+        <v>-0.6593</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.385</v>
+        <v>-0.2128</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1189</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. DIAZ</t>
+          <t>J. BELEMENE-DZABATOU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9537</v>
+        <v>-2.4356</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2247</v>
+        <v>-2.6657</v>
       </c>
       <c r="F21" t="n">
-        <v>0.271</v>
+        <v>0.2302</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5079</v>
+        <v>-1.9716</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6153</v>
+        <v>-1.453</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1231</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2455</v>
+        <v>-1.1144</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4464</v>
+        <v>-1.6243</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2009</v>
+        <v>0.51</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2624</v>
+        <v>-0.8573</v>
       </c>
       <c r="N21" t="n">
-        <v>1.0617</v>
+        <v>0.1714</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.324</v>
+        <v>-1.0286</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.3216</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2027</v>
+        <v>-1.1014</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2027</v>
+        <v>2.423</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4458</v>
+        <v>-0.6667</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7765</v>
+        <v>-0.45</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6693</v>
+        <v>-0.2167</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.1189</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.1189</v>
       </c>
     </row>
     <row r="22">
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.815099999999999</v>
+        <v>-2.471800000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>2.6298</v>
+        <v>2.629799999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.4449</v>
+        <v>-5.101500000000001</v>
       </c>
       <c r="G22" t="n">
         <v>1.3756</v>
       </c>
       <c r="H22" t="n">
-        <v>6.2904</v>
+        <v>6.290399999999999</v>
       </c>
       <c r="I22" t="n">
         <v>-4.914899999999999</v>
@@ -2149,13 +2149,13 @@
         <v>1.4524</v>
       </c>
       <c r="L22" t="n">
-        <v>9.613300000000001</v>
+        <v>9.613299999999999</v>
       </c>
       <c r="M22" t="n">
         <v>-9.69</v>
       </c>
       <c r="N22" t="n">
-        <v>4.8381</v>
+        <v>4.838100000000001</v>
       </c>
       <c r="O22" t="n">
         <v>-14.5281</v>
@@ -2170,13 +2170,13 @@
         <v>16.5205</v>
       </c>
       <c r="S22" t="n">
-        <v>-8.490499999999999</v>
+        <v>-6.1474</v>
       </c>
       <c r="T22" t="n">
         <v>-4.2812</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.2093</v>
+        <v>-1.8662</v>
       </c>
       <c r="V22" t="n">
         <v>-5.4096</v>
